--- a/(枠)◯年度一式/薬品・整備記録.xlsx
+++ b/(枠)◯年度一式/薬品・整備記録.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFCD1240-CE6E-419F-B964-7BFDB82099F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E7090C-4D58-4678-A668-4A342DCD1D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="720" windowWidth="15120" windowHeight="15480" tabRatio="819" activeTab="3" xr2:uid="{2AD8DE8C-9547-419C-90AE-293E0C98334E}"/>
+    <workbookView xWindow="0" yWindow="765" windowWidth="20670" windowHeight="14715" tabRatio="819" xr2:uid="{2AD8DE8C-9547-419C-90AE-293E0C98334E}"/>
   </bookViews>
   <sheets>
     <sheet name="薬品・消耗品" sheetId="1" r:id="rId1"/>
@@ -774,10 +774,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="178" formatCode="mm/dd"/>
-    <numFmt numFmtId="180" formatCode="#,##0_);[Red]\(#,##0\)"/>
-    <numFmt numFmtId="182" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="183" formatCode="#,##0_ "/>
+    <numFmt numFmtId="176" formatCode="mm/dd"/>
+    <numFmt numFmtId="177" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="179" formatCode="#,##0_ "/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -1003,7 +1003,7 @@
   </cellStyleXfs>
   <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1015,19 +1015,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1039,22 +1039,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1072,22 +1072,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1096,22 +1096,22 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1123,13 +1123,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1150,10 +1150,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1165,19 +1165,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1186,7 +1186,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1198,7 +1198,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1213,7 +1213,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1222,7 +1222,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1231,31 +1231,46 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1266,21 +1281,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3025,6 +3025,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="H38:I38"/>
@@ -3032,12 +3038,6 @@
     <mergeCell ref="L38:M38"/>
     <mergeCell ref="J38:K38"/>
     <mergeCell ref="D38:E38"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="J3:K3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
@@ -4078,14 +4078,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="D2:F2"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="D2:F2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
@@ -4600,46 +4600,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
     </row>
     <row r="2" spans="1:13" s="31" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90" t="s">
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90" t="s">
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90" t="s">
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
     </row>
     <row r="3" spans="1:13" s="31" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="27"/>
@@ -4877,11 +4877,11 @@
       <c r="A14" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="92">
+      <c r="B14" s="87">
         <f>D13+G13+J13+M13</f>
         <v>0</v>
       </c>
-      <c r="C14" s="93"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="38" t="s">
         <v>30</v>
       </c>
@@ -4896,39 +4896,39 @@
       <c r="M14" s="34"/>
     </row>
     <row r="15" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="87"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="91"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="92"/>
     </row>
     <row r="16" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="39"/>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88" t="s">
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="88"/>
-      <c r="H16" s="88"/>
-      <c r="I16" s="88" t="s">
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="88"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="88"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="93"/>
     </row>
     <row r="17" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="39"/>
@@ -4959,10 +4959,10 @@
       <c r="K17" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L17" s="88" t="s">
+      <c r="L17" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="M17" s="88"/>
+      <c r="M17" s="93"/>
     </row>
     <row r="18" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="39" t="s">
@@ -4986,11 +4986,11 @@
         <v>0</v>
       </c>
       <c r="K18" s="41"/>
-      <c r="L18" s="89">
+      <c r="L18" s="84">
         <f>D18+G18+J18</f>
         <v>0</v>
       </c>
-      <c r="M18" s="89"/>
+      <c r="M18" s="84"/>
     </row>
     <row r="19" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="39" t="s">
@@ -5014,11 +5014,11 @@
         <v>0</v>
       </c>
       <c r="K19" s="41"/>
-      <c r="L19" s="89">
+      <c r="L19" s="84">
         <f>D19+G19+J19</f>
         <v>0</v>
       </c>
-      <c r="M19" s="89"/>
+      <c r="M19" s="84"/>
     </row>
     <row r="20" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="39" t="s">
@@ -5042,11 +5042,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="41"/>
-      <c r="L20" s="89">
+      <c r="L20" s="84">
         <f>D20+G20+J20</f>
         <v>0</v>
       </c>
-      <c r="M20" s="89"/>
+      <c r="M20" s="84"/>
     </row>
     <row r="21" spans="2:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B21" s="42" t="s">
@@ -5064,30 +5064,30 @@
         <v>0</v>
       </c>
       <c r="K21" s="43"/>
-      <c r="L21" s="85">
+      <c r="L21" s="90">
         <f>D21+G21+J21</f>
         <v>0</v>
       </c>
-      <c r="M21" s="85"/>
+      <c r="M21" s="90"/>
     </row>
     <row r="22" spans="2:13" ht="21.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B22" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="84">
+      <c r="C22" s="89">
         <f>SUM(L18:L20)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
     </row>
     <row r="23" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="24" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -5114,13 +5114,6 @@
     <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
     <mergeCell ref="C22:M22"/>
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="B15:L15"/>
@@ -5131,6 +5124,13 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="I16:K16"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A3:A6">
@@ -5322,12 +5322,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C27:D27"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="C27:D27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
